--- a/growth-hub/sozluk/sozluk.xlsx
+++ b/growth-hub/sozluk/sozluk.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kılavuz" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yayıncılar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yayın Türleri" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sektörler" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fiyat Tipleri" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametreler" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Kılavuz" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Yayıncılar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Yayın Türleri" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sektörler" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fiyat Tipleri" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Parametreler" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Yayıncılar'!$A$1:$G$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yayın Türleri'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yayın Türleri'!$A$1:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sektörler'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fiyat Tipleri'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parametreler'!$A$1:$F$11</definedName>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +132,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2297,7 +2298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2308,6 +2309,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2351,6 +2353,11 @@
           <t>Not</t>
         </is>
       </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Standart reklam modeli</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -2387,6 +2394,11 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Arama</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -2423,6 +2435,11 @@
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Atlanamayan preroll</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -2459,6 +2476,11 @@
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Non-skippable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2495,6 +2517,11 @@
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Non-skippable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2531,6 +2558,11 @@
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Atlanamayan jenerik</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2567,6 +2599,11 @@
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>CTV</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2603,6 +2640,11 @@
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Skippable video</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2639,6 +2681,11 @@
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>TrueView</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2675,6 +2722,11 @@
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Thruplay</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2711,6 +2763,11 @@
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Skippable video</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2747,6 +2804,11 @@
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>TrueView</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2783,6 +2845,11 @@
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>TrueView</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2819,6 +2886,11 @@
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Skippable video</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2855,6 +2927,11 @@
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>TrueView for Action</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2891,6 +2968,11 @@
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Skippable video</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2927,6 +3009,11 @@
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Top View</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2963,6 +3050,11 @@
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Top Feed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2999,6 +3091,11 @@
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Masthead</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -3035,6 +3132,11 @@
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Masthead</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3071,6 +3173,11 @@
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Oyun içi rich media</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3107,6 +3214,11 @@
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Attention Accelerator</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -3143,6 +3255,11 @@
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Oyun içi video</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -3179,6 +3296,11 @@
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Oyun içi rich media</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3215,6 +3337,11 @@
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Preroll</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -3251,6 +3378,11 @@
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Preroll &amp; Liveroll</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3287,6 +3419,11 @@
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Preroll</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -3323,6 +3460,11 @@
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Preroll</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3359,6 +3501,11 @@
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Ses</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3395,6 +3542,11 @@
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Alt bant</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3431,6 +3583,11 @@
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Partner sales</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3467,6 +3624,11 @@
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Endcard + BLS</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3503,6 +3665,11 @@
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Timeline takeover</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -3539,6 +3706,11 @@
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Sponsor ürün</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -3575,6 +3747,11 @@
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>3D kreatör alt bant</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -3611,6 +3788,11 @@
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Line-up</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -3647,6 +3829,11 @@
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Reach block</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -3683,6 +3870,11 @@
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>3D kreatör alt bant</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -3719,6 +3911,11 @@
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Reach block</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -3755,6 +3952,11 @@
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Endcard + BLS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -3791,6 +3993,11 @@
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Interactive endcard</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -3827,6 +4034,11 @@
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -3863,6 +4075,11 @@
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>First view + spotlight</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -3899,6 +4116,11 @@
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -3935,6 +4157,11 @@
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>CPAS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -3971,6 +4198,11 @@
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -4007,6 +4239,11 @@
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Banner CPC</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -4043,6 +4280,11 @@
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Display CPC</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -4079,6 +4321,11 @@
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Native CPC</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -4115,6 +4362,11 @@
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -4151,6 +4403,11 @@
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -4187,6 +4444,11 @@
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Banner CPC</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4196,7 +4458,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:I52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4702,7 +4964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5047,8 +5309,193 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>karne_kirilim</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>seçim</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Karnenin ayrıştığı en ince kırılım</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>"reklam modeli" yapılırsa puan reklam modeli bazında ayrışır; "ana tür" bugünkü davranış</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>CDO</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>reklam_modelleri</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>3D kreatör alt bant | Alt bant | Arama | Atlanamayan jenerik | Atlanamayan preroll | Attention Accelerator | Banner CPC | Conversion | CPAS | CTV | Display CPC | Endcard + BLS | Engagement | First view + spotlight | Interactive endcard | Line-up | Masthead | Native CPC | Non-skippable | Oyun içi rich media | Oyun içi video | Partner sales | Post | Preroll | Preroll &amp; Liveroll | Reach block | Ses | Skippable video | Sponsor ürün | Thruplay | Timeline takeover | Top Feed | Top View | Traffic | TrueView | TrueView for Action</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>liste</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Standart reklam modelleri (arayüz listesi)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Yeni model eklerseniz Yayın Türleri sayfasındaki eşlemeyle uyumlu tutun</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>CDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>cekirdek_min_n</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>satır</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Öneride çekirdek havuza girmek için gereken en az satır</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Büyütürseniz öneri yalnız çok veri olan yayıncıları çekirdeğe alır</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>cekirdek_adet</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Çekirdek havuzdan alınacak en fazla aday</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Küçültürseniz plan daha az yayıncıya yığılır</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>deneme_indeks_esigi</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>puan</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Deneme havuzuna girmek için gereken en az puan/indeks</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Yükseltirseniz yalnız umut vaat eden az-veri yayıncılar denenir</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>deneme_adet</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Deneme havuzundan alınacak en fazla aday</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Deneme payını kaç yayıncıya böleceğini belirler</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Bu sayfadaki değerler teknik ayar değil, ajans politikasıdır. Değiştirmeden önce ekiple konuşun; her değişiklik bir sonraki gece puanlara yansır.</t>
         </is>
